--- a/data/seed/portfolio/L-2024-1067/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-1067/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J188"/>
+  <dimension ref="A1:J169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -540,63 +540,63 @@
       <c r="B8" t="n">
         <v>100</v>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>14359000</v>
-      </c>
-      <c r="D8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n">
+        <v>16115000</v>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nihol Oziq-ovqat Savdo XK</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>336227780</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000612992396001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №1040</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9225</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>85041000</v>
+        <v>115515000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="B9" t="n">
         <v>101</v>
       </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n">
-        <v>2024000</v>
+        <v>4736000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>367434262</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000527107315001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -606,11 +606,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №6086 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Tovar uchun to'lov, hisob-faktura №280 01.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>87065000</v>
+        <v>120251000</v>
       </c>
     </row>
     <row r="10">
@@ -620,312 +620,312 @@
       <c r="B10" t="n">
         <v>102</v>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>9672000</v>
-      </c>
-      <c r="D10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n">
+        <v>4894000</v>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Namangan Meva Eksport AJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>206236289</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000260713386001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №9264</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №262/26 ОТ 02.07.2026</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>77393000</v>
+        <v>125145000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>12694000</v>
+        <v>2421000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Shartnoma №210/26 bo'yicha oldindan to'lov</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №156 02.07.2026, QQS BILAN</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>90087000</v>
+        <v>127566000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>5455000</v>
+        <v>1995000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №4281 за поставленный товар</t>
+          <t>Shartnoma №78/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>95542000</v>
+        <v>129561000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46208</v>
+        <v>46205</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>24600000</v>
+        <v>15662000</v>
       </c>
       <c r="D13" s="2" t="n"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-1067)</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>16307000371917360417</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-1067 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №202/26</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>70942000</v>
+        <v>113899000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B14" t="n">
         <v>106</v>
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>4654000</v>
+        <v>2375000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №116/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №6114 03.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>75596000</v>
+        <v>116274000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B15" t="n">
         <v>107</v>
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>4451000</v>
+        <v>2070000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Andijon Mebel XK</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>218610126</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000313104364001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4071</t>
+          <t>Shartnoma №144/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>80047000</v>
+        <v>118344000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B16" t="n">
         <v>108</v>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n">
-        <v>3346000</v>
-      </c>
+      <c r="C16" s="2" t="n">
+        <v>41801000</v>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Qo'qon Logistik MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>390761727</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000521126139001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Shartnoma №289/26 bo'yicha oldindan to'lov</t>
+          <t>Tovarlar uchun to'lov h/f №9747</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>83393000</v>
+        <v>76543000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46209</v>
+        <v>46208</v>
       </c>
       <c r="B17" t="n">
         <v>109</v>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n">
-        <v>2991000</v>
-      </c>
+      <c r="C17" s="2" t="n">
+        <v>24600000</v>
+      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>351981457</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-1067)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>16307000371917360417</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5689 за поставленный товар</t>
+          <t>Kredit shartnomasi L-2024-1067 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>86384000</v>
+        <v>51943000</v>
       </c>
     </row>
     <row r="18">
@@ -937,35 +937,35 @@
       </c>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n">
-        <v>2260000</v>
+        <v>6417000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Farg'ona Trans Servis XK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>343426215</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000710731535001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №187/26 от 06.07.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №111/26, QQS 12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>88644000</v>
+        <v>58360000</v>
       </c>
     </row>
     <row r="19">
@@ -975,37 +975,37 @@
       <c r="B19" t="n">
         <v>111</v>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>8785000</v>
-      </c>
-      <c r="D19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n">
+        <v>2510000</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Xiva Polimer XK</t>
+          <t>Urganch Non MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>249672389</t>
+          <t>361012663</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000254901258001</t>
+          <t>20208000310436449001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №239/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №318 06.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>79859000</v>
+        <v>60870000</v>
       </c>
     </row>
     <row r="20">
@@ -1015,58 +1015,63 @@
       <c r="B20" t="n">
         <v>112</v>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>28480000</v>
-      </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n">
+        <v>1645000</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Farg'ona Trans Servis XK</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>343426215</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000710731535001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Tovar uchun to'lov, h/f №1790 06.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>51379000</v>
+        <v>62515000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n">
-        <v>93900000</v>
-      </c>
+      <c r="C21" s="2" t="n">
+        <v>11141000</v>
+      </c>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer MChJ</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>312872029</t>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000012531452001</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1076,37 +1081,37 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5824 за поставленный товар</t>
+          <t>Оплата за сырье по договору №157/26 от 06.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>145279000</v>
+        <v>51374000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n">
-        <v>2999000</v>
-      </c>
+      <c r="C22" s="2" t="n">
+        <v>14373000</v>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tong Metall MChJ</t>
+          <t>Urganch Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>372693813</t>
+          <t>260870909</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000832203775001</t>
+          <t>20208000019772708001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1116,131 +1121,126 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8883 от 07.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №112/26</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>148278000</v>
+        <v>37001000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n">
-        <v>2079000</v>
-      </c>
+      <c r="C23" s="2" t="n">
+        <v>25558000</v>
+      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №753 от 07.07.2026, в т.ч. НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №50/26, QQS bilan</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>150357000</v>
+        <v>11443000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>7097000</v>
+        <v>27549000</v>
       </c>
       <c r="D24" s="2" t="n"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Xiva Polimer XK</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>249672389</t>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000254901258001</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №205/26</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №81/26</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>143260000</v>
+        <v>-16106000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n">
-        <v>6498000</v>
-      </c>
+      <c r="C25" s="2" t="n">
+        <v>28480000</v>
+      </c>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>367434262</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000527107315001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №54/26 от 08.07.2026</t>
+          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>149758000</v>
+        <v>-44586000</v>
       </c>
     </row>
     <row r="26">
@@ -1256,31 +1256,31 @@
       <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Omad Qurilish MChJ</t>
+          <t>Sarbon Qurilish MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>281323691</t>
+          <t>296114067</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000893848717001</t>
+          <t>20208000351645437001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Аренда помещения за июль, дог. №77/23</t>
+          <t>Аренда помещения за июль, дог. №32/25</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>146868000</v>
+        <v>-47476000</v>
       </c>
     </row>
     <row r="27">
@@ -1292,35 +1292,35 @@
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>4164000</v>
+        <v>3104000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №146/26 от 09.07.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2377</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>151032000</v>
+        <v>-44372000</v>
       </c>
     </row>
     <row r="28">
@@ -1330,117 +1330,117 @@
       <c r="B28" t="n">
         <v>120</v>
       </c>
-      <c r="C28" s="2" t="n">
-        <v>10247000</v>
-      </c>
-      <c r="D28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n">
+        <v>2206000</v>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Namangan Meva Eksport AJ</t>
+          <t>Zafar Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>206236289</t>
+          <t>287202980</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000260713386001</t>
+          <t>20208000253145244001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №97/26 от 09.07.2026, НДС 12%</t>
+          <t>Предоплата за товар по договору №164/26 от 09.07.2026</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>140785000</v>
+        <v>-42166000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46213</v>
+        <v>46212</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n">
-        <v>18443000</v>
-      </c>
+      <c r="C29" s="2" t="n">
+        <v>5427000</v>
+      </c>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4396 10.07.2026, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №199/26</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>159228000</v>
+        <v>-47593000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>28983000</v>
-      </c>
-      <c r="D30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n">
+        <v>4686000</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Xiva Polimer XK</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>249672389</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000254901258001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №12/26</t>
+          <t>Shartnoma №212/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>130245000</v>
+        <v>-42907000</v>
       </c>
     </row>
     <row r="31">
@@ -1452,35 +1452,35 @@
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n">
-        <v>11422000</v>
+        <v>3702000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4530</t>
+          <t>Оплата за товар по счет-фактуре №8541 от 13.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>141667000</v>
+        <v>-39205000</v>
       </c>
     </row>
     <row r="32">
@@ -1492,35 +1492,35 @@
       </c>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n">
-        <v>6982000</v>
+        <v>3062000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Toshkent Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>367434262</t>
+          <t>274534012</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000527107315001</t>
+          <t>20208000445565106001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5119 за пставленный товар</t>
+          <t>Shartnoma №78/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>148649000</v>
+        <v>-36143000</v>
       </c>
     </row>
     <row r="33">
@@ -1532,35 +1532,35 @@
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>4630000</v>
+        <v>2969000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Yulduz Logistik MChJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>324503118</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000824779806001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №39/26, НДС 12%</t>
+          <t>Yetkazilgn tovar uchun to'lov h/f №9083</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>153279000</v>
+        <v>-33174000</v>
       </c>
     </row>
     <row r="34">
@@ -1572,35 +1572,35 @@
       </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n">
-        <v>3158000</v>
+        <v>2423000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer MChJ</t>
+          <t>Kattaqo'rg'on Plastik MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>312872029</t>
+          <t>323628962</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000012531452001</t>
+          <t>20208000071338667001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9479 13.07.2026, QQS bilan</t>
+          <t>Shartnoma №199/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>156437000</v>
+        <v>-30751000</v>
       </c>
     </row>
     <row r="35">
@@ -1612,21 +1612,21 @@
       </c>
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="n">
-        <v>2622000</v>
+        <v>1935000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>367434262</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000527107315001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1636,11 +1636,11 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №203/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8393</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>159059000</v>
+        <v>-28816000</v>
       </c>
     </row>
     <row r="36">
@@ -1650,77 +1650,77 @@
       <c r="B36" t="n">
         <v>128</v>
       </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n">
-        <v>2029000</v>
-      </c>
+      <c r="C36" s="2" t="n">
+        <v>8080000</v>
+      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №9716 за поставленный товар</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №266/26</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>161088000</v>
+        <v>-36896000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>3884000</v>
+        <v>46314000</v>
       </c>
       <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Urganch Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>260870909</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000019772708001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Социальный налог за июнь 2026 г.</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №291/26, QQS bilan</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>157204000</v>
+        <v>-83210000</v>
       </c>
     </row>
     <row r="38">
@@ -1731,36 +1731,36 @@
         <v>130</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>3884000</v>
+        <v>13044000</v>
       </c>
       <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>НДФЛ ЗА ИЮНЬ 2026</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №112/26</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>153320000</v>
+        <v>-96254000</v>
       </c>
     </row>
     <row r="39">
@@ -1770,23 +1770,23 @@
       <c r="B39" t="n">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n">
-        <v>6695000</v>
-      </c>
+      <c r="C39" s="2" t="n">
+        <v>30036000</v>
+      </c>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Yulduz Logistik MChJ</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>324503118</t>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000824779806001</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1796,37 +1796,37 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №8/26, НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №1071</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>160015000</v>
+        <v>-126290000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n">
-        <v>3984000</v>
+        <v>7476000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Farg'ona Trans Servis XK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>367434262</t>
+          <t>343426215</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000527107315001</t>
+          <t>20208000710731535001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1836,11 +1836,11 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3449 15.07.2026, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7863 16.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>163999000</v>
+        <v>-118814000</v>
       </c>
     </row>
     <row r="41">
@@ -1850,37 +1850,37 @@
       <c r="B41" t="n">
         <v>133</v>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>46556000</v>
-      </c>
-      <c r="D41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n">
+        <v>2762000</v>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nihol Oziq-ovqat Savdo XK</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>336227780</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000612992396001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №231/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6039 16.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>117443000</v>
+        <v>-116052000</v>
       </c>
     </row>
     <row r="42">
@@ -1891,76 +1891,76 @@
         <v>134</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>94754000</v>
+        <v>3884000</v>
       </c>
       <c r="D42" s="2" t="n"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Termiz Trans Servis XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>233130009</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000990573045001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9491</t>
+          <t>Iyun oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>22689000</v>
+        <v>-119936000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46220</v>
+        <v>46219</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n">
-        <v>12507000</v>
-      </c>
+      <c r="C43" s="2" t="n">
+        <v>3884000</v>
+      </c>
+      <c r="D43" s="2" t="n"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9394 от 17.07.2026, в т.ч. НДС 12%</t>
+          <t>JShDS iyun oyi uchun</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>35196000</v>
+        <v>-123820000</v>
       </c>
     </row>
     <row r="44">
@@ -1972,115 +1972,115 @@
       </c>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n">
-        <v>2408000</v>
+        <v>3464000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer MChJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>312872029</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000012531452001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №2/26 от 17.07.2026</t>
+          <t>Mahsulot uchun to'lov, shartn. №137/26, QQS 12%</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>37604000</v>
+        <v>-120356000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46223</v>
+        <v>46220</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n">
-        <v>34426000</v>
-      </c>
+      <c r="C45" s="2" t="n">
+        <v>4648000</v>
+      </c>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>367434262</t>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000527107315001</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9794 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за упаковочные материлы, с/ф №1641</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>72030000</v>
+        <v>-125004000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46223</v>
+        <v>46220</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n">
-        <v>13086000</v>
-      </c>
+      <c r="C46" s="2" t="n">
+        <v>8795000</v>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №51/26, QQS 12%</t>
+          <t>Оплата за транспортные услуги по дог. №53/26</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>85116000</v>
+        <v>-133799000</v>
       </c>
     </row>
     <row r="47">
@@ -2090,37 +2090,37 @@
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>6429000</v>
-      </c>
-      <c r="D47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n">
+        <v>85302000</v>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Xiva Polimer XK</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>249672389</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000254901258001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6028</t>
+          <t>Shartnoma №108/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>78687000</v>
+        <v>-48497000</v>
       </c>
     </row>
     <row r="48">
@@ -2130,37 +2130,37 @@
       <c r="B48" t="n">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>7621000</v>
-      </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n">
+        <v>22961000</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Xiva Polimer XK</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>249672389</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000254901258001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №201/26</t>
+          <t>Предоплата за товар по договору №80/26 от 20.07.2026</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>71066000</v>
+        <v>-25536000</v>
       </c>
     </row>
     <row r="49">
@@ -2170,23 +2170,23 @@
       <c r="B49" t="n">
         <v>141</v>
       </c>
-      <c r="C49" s="2" t="n">
-        <v>22982000</v>
-      </c>
-      <c r="D49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n">
+        <v>2508000</v>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Termiz Trans Servis XK</t>
+          <t>Farg'ona Trans Servis XK</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>233130009</t>
+          <t>343426215</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000990573045001</t>
+          <t>20208000710731535001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2196,77 +2196,77 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №4724</t>
+          <t>Tovar uchun to'lov, hisob-faktura №947 20.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>48084000</v>
+        <v>-23028000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>34287000</v>
+        <v>16216000</v>
       </c>
       <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Xiva Polimer XK</t>
+          <t>Shodlik Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>249672389</t>
+          <t>299753444</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000254901258001</t>
+          <t>20208000331066892001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6480</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №208/26</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>13797000</v>
+        <v>-39244000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n">
-        <v>29823000</v>
-      </c>
+      <c r="C51" s="2" t="n">
+        <v>20202000</v>
+      </c>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer MChJ</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>312872029</t>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000012531452001</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2276,11 +2276,11 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5285 за поставленный товар</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №151/26, QQS bilan</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>43620000</v>
+        <v>-59446000</v>
       </c>
     </row>
     <row r="52">
@@ -2290,277 +2290,277 @@
       <c r="B52" t="n">
         <v>144</v>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>7404000</v>
-      </c>
-      <c r="D52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n">
+        <v>5690000</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Xiva Polimer XK</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>249672389</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000254901258001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №81/26 от 22.07.2026, НДС 12%</t>
+          <t>Yetkazilgan tovar chun to'lov h/f №7074</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>36216000</v>
+        <v>-53756000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
-      <c r="C53" s="2" t="n">
-        <v>4821000</v>
-      </c>
-      <c r="D53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n">
+        <v>4277000</v>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>НДС за июнь 2026 г.</t>
+          <t>Tovar uchun to'lov, hisob-faktura №268 22.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>31395000</v>
+        <v>-49479000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
-      <c r="C54" s="2" t="n">
-        <v>6050000</v>
-      </c>
-      <c r="D54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n">
+        <v>2876000</v>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Xiva Polimer XK</t>
+          <t>Toshkent Trans Servis XK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>249672389</t>
+          <t>269381348</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000254901258001</t>
+          <t>20208000220377573001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №24/26 от 23.07.2026, НДС 12%</t>
+          <t>Shartnoma №230/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>25345000</v>
+        <v>-46603000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46227</v>
+        <v>46226</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>9963000</v>
+        <v>3481000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Farg'ona Trans Servis XK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>343426215</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000710731535001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8111 за поставленный товар</t>
+          <t>Предоплата за товар по дог. №249/26 от 23.07.2026</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>35308000</v>
+        <v>-43122000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46227</v>
+        <v>46226</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1806000</v>
+        <v>4736000</v>
       </c>
       <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000737739460001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov iyul</t>
+          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>33502000</v>
+        <v>-47858000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n">
-        <v>9668000</v>
-      </c>
+      <c r="C57" s="2" t="n">
+        <v>1806000</v>
+      </c>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000635963108001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №258/26, НДС 12%</t>
+          <t>Оплата за электроэнергию за июль 2026 г.</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>43170000</v>
+        <v>-49664000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n">
-        <v>8287000</v>
-      </c>
+      <c r="C58" s="2" t="n">
+        <v>30571000</v>
+      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Omad Meva Eksport AJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>367434262</t>
+          <t>215107383</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000527107315001</t>
+          <t>20208000575856861001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6481 за поставленный товар</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №114/26, QQS bilan</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>51457000</v>
+        <v>-80235000</v>
       </c>
     </row>
     <row r="59">
@@ -2572,35 +2572,35 @@
       </c>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n">
-        <v>5922000</v>
+        <v>58055000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Andijon Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>367434262</t>
+          <t>378878168</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000527107315001</t>
+          <t>20208000740879456001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №183 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9670 27.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>57379000</v>
+        <v>-22180000</v>
       </c>
     </row>
     <row r="60">
@@ -2612,35 +2612,35 @@
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>5024000</v>
+        <v>36516000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Farg'ona Trans Servis XK</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>343426215</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000710731535001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №761 27.07.2026, QQS BILAN</t>
+          <t>Mahsulot uchun to'lov, shartnoma №78/26, QQS 12%</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>62403000</v>
+        <v>14336000</v>
       </c>
     </row>
     <row r="61">
@@ -2652,35 +2652,35 @@
       </c>
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n">
-        <v>3720000</v>
+        <v>17118000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Kattaqo'rg'on Plastik MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>323628962</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000071338667001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №149/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1582</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>66123000</v>
+        <v>31454000</v>
       </c>
     </row>
     <row r="62">
@@ -2692,101 +2692,101 @@
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>3223000</v>
+        <v>9354000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Andijon Mebel XK</t>
+          <t>Farg'ona Trans Servis XK</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>218610126</t>
+          <t>343426215</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000313104364001</t>
+          <t>20208000710731535001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №202/26 от 27.07.2026</t>
+          <t>Shartnoma №78/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>69346000</v>
+        <v>40808000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>7026000</v>
+        <v>8148000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Tong Metall MChJ</t>
+          <t>Zafar Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>372693813</t>
+          <t>287202980</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000832203775001</t>
+          <t>20208000253145244001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9635 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №896</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>76372000</v>
+        <v>48956000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46232</v>
+        <v>46230</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>38107000</v>
+        <v>5834000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>367434262</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000527107315001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2796,117 +2796,117 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №160/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6751 27.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>114479000</v>
+        <v>54790000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>5732000</v>
+        <v>5290000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №235/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №51/26, НДС 12%</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>120211000</v>
+        <v>60080000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
-      <c r="C66" s="2" t="n">
-        <v>17795000</v>
-      </c>
-      <c r="D66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n">
+        <v>4388000</v>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Nihol Oziq-ovqat Savdo XK</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>336227780</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000612992396001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3232</t>
+          <t>Shartnoma №117/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>102416000</v>
+        <v>64468000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46234</v>
+        <v>46230</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
       <c r="C67" s="2" t="n"/>
       <c r="D67" s="2" t="n">
-        <v>5358000</v>
+        <v>4035000</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>367434262</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000527107315001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2916,307 +2916,312 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №118/26 от 31.07.2026</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №6323</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>107774000</v>
+        <v>68503000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46234</v>
+        <v>46230</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
-      <c r="C68" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n">
+        <v>1745000</v>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Shartnoma №216/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>107474000</v>
+        <v>70248000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46237</v>
+        <v>46231</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>26739000</v>
+        <v>3674000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Zafar Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>287202980</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000253145244001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №168/26 от 03.08.2026</t>
+          <t>Shartnoma №154/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>134213000</v>
+        <v>73922000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46237</v>
+        <v>46231</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
       <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="n">
-        <v>11326000</v>
+        <v>3195000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7775 03.08.2026, QQS bilan</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №44/26, QQS 12%</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>145539000</v>
+        <v>77117000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46237</v>
+        <v>46233</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
       <c r="C71" s="2" t="n"/>
       <c r="D71" s="2" t="n">
-        <v>7120000</v>
+        <v>1737000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2223 от 03.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по с/ф №8105 за поставленный товар</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>152659000</v>
+        <v>78854000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
       <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="n">
-        <v>4641000</v>
+        <v>21274000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №35/26 от 03.08.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9124</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>157300000</v>
+        <v>100128000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
-      <c r="C73" s="2" t="n">
-        <v>39878000</v>
-      </c>
-      <c r="D73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n">
+        <v>4242000</v>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nihol Oziq-ovqat Savdo XK</t>
+          <t>Andijon Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>336227780</t>
+          <t>378878168</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000612992396001</t>
+          <t>20208000740879456001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №153/26, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5213</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>117422000</v>
+        <v>104370000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46238</v>
+        <v>46234</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n">
-        <v>7808000</v>
-      </c>
+      <c r="C74" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D74" s="2" t="n"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>351981457</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №261/26 от 04.08.2026</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>125230000</v>
+        <v>104070000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46239</v>
+        <v>46237</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
-      <c r="C75" s="2" t="n">
-        <v>23512000</v>
-      </c>
-      <c r="D75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n">
+        <v>8165000</v>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Kattaqo'rg'on Plastik MChJ</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>323628962</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000071338667001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3226,312 +3231,307 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ish haqi, reestr №29</t>
+          <t>Shartnoma №288/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>101718000</v>
+        <v>112235000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46239</v>
+        <v>46237</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>24600000</v>
-      </c>
-      <c r="D76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n">
+        <v>3138000</v>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-1067)</t>
+          <t>Farg'ona Trans Servis XK</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>343426215</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>16307000371917360417</t>
+          <t>20208000710731535001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-1067 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата за продукцию по дог. №135/26, НДС 12%</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>77118000</v>
+        <v>115373000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46241</v>
+        <v>46237</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
-      <c r="C77" s="2" t="n">
-        <v>2386000</v>
-      </c>
-      <c r="D77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n">
+        <v>1970000</v>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Omad Qurilish MChJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>281323691</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000893848717001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Арендная плата за август 2026 г. по договору №77/23</t>
+          <t>Mahsulot uchun to'lov, shartnoma №142/26, QQS 12%</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>74732000</v>
+        <v>117343000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
-      <c r="C78" s="2" t="n"/>
-      <c r="D78" s="2" t="n">
-        <v>19284000</v>
-      </c>
+      <c r="C78" s="2" t="n">
+        <v>3190000</v>
+      </c>
+      <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №258/26, НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №230/26</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>94016000</v>
+        <v>114153000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>105554000</v>
+        <v>8456000</v>
       </c>
       <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Xiva Polimer XK</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>249672389</t>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000254901258001</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №110/26</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №2/26</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>-11538000</v>
+        <v>105697000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46245</v>
+        <v>46239</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n">
-        <v>11496000</v>
-      </c>
+      <c r="C80" s="2" t="n">
+        <v>7669000</v>
+      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Tong Metall MChJ</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>372693813</t>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000832203775001</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №119/26, НДС 12%</t>
+          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №166/26, QQS BILAN</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>-42000</v>
+        <v>98028000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46245</v>
+        <v>46239</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
-      <c r="C81" s="2" t="n"/>
-      <c r="D81" s="2" t="n">
-        <v>5373000</v>
-      </c>
+      <c r="C81" s="2" t="n">
+        <v>23512000</v>
+      </c>
+      <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>367434262</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000527107315001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №272/26, QQS 12%</t>
+          <t>Iyul oyi uchun ish haqi, reestr №5831</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>5331000</v>
+        <v>74516000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46245</v>
+        <v>46239</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n">
-        <v>4405000</v>
-      </c>
+      <c r="C82" s="2" t="n">
+        <v>24600000</v>
+      </c>
+      <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>351981457</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-1067)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>16307000371917360417</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Shartnoma №216/26 bo'yicha oldindan to'lov</t>
+          <t>Kredit shartnomasi L-2024-1067 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>9736000</v>
+        <v>49916000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46247</v>
+        <v>46240</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="2" t="n">
-        <v>28695000</v>
-      </c>
+      <c r="C83" s="2" t="n">
+        <v>7860000</v>
+      </c>
+      <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Namangan Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>361039787</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000635048122001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3541,77 +3541,77 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9476 за поставленный товар</t>
+          <t>Tovarlar uchun to'lov h/f №6064</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>38431000</v>
+        <v>42056000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46247</v>
+        <v>46241</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
-      <c r="C84" s="2" t="n">
-        <v>36771000</v>
-      </c>
-      <c r="D84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n">
+        <v>1448000</v>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Nihol Oziq-ovqat Savdo XK</t>
+          <t>Kattaqo'rg'on Plastik MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>336227780</t>
+          <t>323628962</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000612992396001</t>
+          <t>20208000071338667001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №6771</t>
+          <t>Yetkazilgan tovar uchun to'lov /f №6982</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1660000</v>
+        <v>43504000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46248</v>
+        <v>46244</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
       <c r="C85" s="2" t="n"/>
       <c r="D85" s="2" t="n">
-        <v>14308000</v>
+        <v>8082000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Farg'ona Metall MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>367434262</t>
+          <t>250311888</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000527107315001</t>
+          <t>20208000477980626001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3621,651 +3621,651 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3638 от 14.08.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №81/26, QQS 12%</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>15968000</v>
+        <v>51586000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46248</v>
+        <v>46244</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n">
-        <v>7984000</v>
+        <v>1279000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Kattaqo'rg'on Plastik MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>367434262</t>
+          <t>323628962</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000527107315001</t>
+          <t>20208000071338667001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Shartnoma №124/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №802 10.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>23952000</v>
+        <v>52865000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n">
-        <v>9678000</v>
-      </c>
+      <c r="C87" s="2" t="n">
+        <v>2386000</v>
+      </c>
+      <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer MChJ</t>
+          <t>Sarbon Qurilish MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>312872029</t>
+          <t>296114067</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000012531452001</t>
+          <t>20208000351645437001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №26/26, НДС 12%</t>
+          <t>Ijara haqi avgust oyi uchun, shartnoma №32/25</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>33630000</v>
+        <v>50479000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n">
-        <v>5675000</v>
-      </c>
+      <c r="C88" s="2" t="n">
+        <v>2522000</v>
+      </c>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Qo'qon Logistik MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>390761727</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000521126139001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №260/26, НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №224/26</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>39305000</v>
+        <v>47957000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46251</v>
+        <v>46245</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
       <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="n">
-        <v>5524000</v>
+        <v>9733000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Zafar Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>287202980</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000253145244001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №1560 ОТ 17.08.2026, В Т.Ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №6886 11.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>44829000</v>
+        <v>57690000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46251</v>
+        <v>46245</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
-      <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n">
-        <v>3912000</v>
-      </c>
+      <c r="C90" s="2" t="n">
+        <v>44983000</v>
+      </c>
+      <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8445 от 17.0.2026, в т.ч. НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №252/26</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>48741000</v>
+        <v>12707000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46251</v>
+        <v>46246</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>3206000</v>
+        <v>2648000</v>
       </c>
       <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Urganch Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>260870909</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000019772708001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Социальный налог за июль 2026 г.</t>
+          <t>Tovarlar uchun to'lov h/f №4814</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>45535000</v>
+        <v>10059000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>3206000</v>
+        <v>6045000</v>
       </c>
       <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>JShDS iyul oyi uchun</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №126/26, QQS bilan</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>42329000</v>
+        <v>4014000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
-      <c r="C93" s="2" t="n">
-        <v>9345000</v>
-      </c>
-      <c r="D93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n">
+        <v>2732000</v>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Shahrisabz Dori-Darmon MChJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>309788781</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000817408794001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №120/26</t>
+          <t>Tovar uchun to'lov, h/f №7196 14.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>32984000</v>
+        <v>6746000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
-      <c r="C94" s="2" t="n">
-        <v>14337000</v>
-      </c>
-      <c r="D94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n">
+        <v>1151000</v>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Xiva Polimer XK</t>
+          <t>Toshkent Trans Servis XK</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>249672389</t>
+          <t>269381348</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000254901258001</t>
+          <t>20208000220377573001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №133/26</t>
+          <t>Shartnoma №230/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>18647000</v>
+        <v>7897000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46252</v>
+        <v>46248</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
-      <c r="C95" s="2" t="n"/>
-      <c r="D95" s="2" t="n">
-        <v>8243000</v>
-      </c>
+      <c r="C95" s="2" t="n">
+        <v>3113000</v>
+      </c>
+      <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Omad Meva Eksport AJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>215107383</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000575856861001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Shartnoma №297/26 bo'yicha oldindan to'lov</t>
+          <t>Tovarlar uchun to'lov h/f №5278</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>26890000</v>
+        <v>4784000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>14973000</v>
+        <v>3206000</v>
       </c>
       <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Shahrisabz Dori-Darmon MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>309788781</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000817408794001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №28/26 от 19.08.2026, НДС 12%</t>
+          <t>Iyul oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>11917000</v>
+        <v>1578000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46253</v>
+        <v>46251</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>18101000</v>
+        <v>3206000</v>
       </c>
       <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Xiva Polimer XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>249672389</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000254901258001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №326</t>
+          <t>Jismoniy shaxslar daromad solig'i iyul 2026</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>-6184000</v>
+        <v>-1628000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
       <c r="C98" s="2" t="n"/>
       <c r="D98" s="2" t="n">
-        <v>4588000</v>
+        <v>5629000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Farg'ona Metall MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>250311888</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000477980626001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №233/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №250/26, QQS 12%</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>-1596000</v>
+        <v>4001000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46255</v>
+        <v>46253</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
-      <c r="C99" s="2" t="n"/>
-      <c r="D99" s="2" t="n">
-        <v>4800000</v>
-      </c>
+      <c r="C99" s="2" t="n">
+        <v>6031000</v>
+      </c>
+      <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Omad Meva Eksport AJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>215107383</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000575856861001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №105/26 от 21.08.2026</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №75/26</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>3204000</v>
+        <v>-2030000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
       <c r="C100" s="2" t="n"/>
       <c r="D100" s="2" t="n">
-        <v>4064000</v>
+        <v>255900000</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Shartnoma №291/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartn. №24/26, QQS 12%</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>7268000</v>
+        <v>253870000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
-      <c r="C101" s="2" t="n">
-        <v>7461000</v>
-      </c>
-      <c r="D101" s="2" t="n"/>
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" s="2" t="n">
+        <v>1443000</v>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Xiva Polimer XK</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>249672389</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000254901258001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №138/26 от 21.08.2026, НДС 12%</t>
+          <t>Shartnoma №168/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>-193000</v>
+        <v>255313000</v>
       </c>
     </row>
     <row r="102">
@@ -4275,37 +4275,37 @@
       <c r="B102" t="n">
         <v>194</v>
       </c>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="2" t="n">
-        <v>12864000</v>
-      </c>
+      <c r="C102" s="2" t="n">
+        <v>3764000</v>
+      </c>
+      <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Andijon Mebel XK</t>
+          <t>Namangan Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>218610126</t>
+          <t>361039787</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000313104364001</t>
+          <t>20208000635048122001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №214 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №9095</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>12671000</v>
+        <v>251549000</v>
       </c>
     </row>
     <row r="103">
@@ -4315,37 +4315,37 @@
       <c r="B103" t="n">
         <v>195</v>
       </c>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n">
-        <v>7379000</v>
-      </c>
+      <c r="C103" s="2" t="n">
+        <v>3810000</v>
+      </c>
+      <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Tong Metall MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>372693813</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000832203775001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №256/26, QQS 12%</t>
+          <t>QQS iyul 2026 uchun</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>20050000</v>
+        <v>247739000</v>
       </c>
     </row>
     <row r="104">
@@ -4355,37 +4355,37 @@
       <c r="B104" t="n">
         <v>196</v>
       </c>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n">
-        <v>4362000</v>
-      </c>
+      <c r="C104" s="2" t="n">
+        <v>4473000</v>
+      </c>
+      <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer MChJ</t>
+          <t>Qo'qon Logistik MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>312872029</t>
+          <t>390761727</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000012531452001</t>
+          <t>20208000521126139001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Shartnoma №158/26 bo'yicha oldindan to'lov</t>
+          <t>Tovarlar uchun to'lov h/f №4568</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>24412000</v>
+        <v>243266000</v>
       </c>
     </row>
     <row r="105">
@@ -4396,196 +4396,196 @@
         <v>197</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>3988000</v>
+        <v>152740000</v>
       </c>
       <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qo'qon Logistik MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>390761727</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000521126139001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июль</t>
+          <t>Tovarlar uchun to'lov h/f №6511</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>20424000</v>
+        <v>90526000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
-      <c r="C106" s="2" t="n">
-        <v>26469000</v>
-      </c>
-      <c r="D106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n">
+        <v>2055000</v>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Xiva Polimer XK</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>249672389</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000254901258001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №7674</t>
+          <t>Оплата за продукцию по договору №273/26, НДС 12%</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>-6045000</v>
+        <v>92581000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
-      <c r="C107" s="2" t="n"/>
-      <c r="D107" s="2" t="n">
-        <v>8638000</v>
-      </c>
+      <c r="C107" s="2" t="n">
+        <v>1491000</v>
+      </c>
+      <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000635963108001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5329 за поставленный товар</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>2593000</v>
+        <v>91090000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
-      <c r="C108" s="2" t="n"/>
-      <c r="D108" s="2" t="n">
-        <v>7450000</v>
-      </c>
+      <c r="C108" s="2" t="n">
+        <v>5795000</v>
+      </c>
+      <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4600 от 25.08.2026, в т.ч. НДС 12%</t>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №149/26</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>10043000</v>
+        <v>85295000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>1491000</v>
-      </c>
-      <c r="D109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n">
+        <v>4109000</v>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000737739460001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Shartnoma №207/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>8552000</v>
+        <v>89404000</v>
       </c>
     </row>
     <row r="110">
@@ -4595,23 +4595,23 @@
       <c r="B110" t="n">
         <v>202</v>
       </c>
-      <c r="C110" s="2" t="n"/>
-      <c r="D110" s="2" t="n">
-        <v>24347000</v>
-      </c>
+      <c r="C110" s="2" t="n">
+        <v>2632000</v>
+      </c>
+      <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer MChJ</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>312872029</t>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000012531452001</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4621,91 +4621,91 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Shartnoma №49/26 bo'yicha oldindan to'lov</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №233/26, QQS bilan</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>32899000</v>
+        <v>86772000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
       <c r="C111" s="2" t="n"/>
       <c r="D111" s="2" t="n">
-        <v>6957000</v>
+        <v>5061000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Zafar Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>287202980</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000253145244001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7357</t>
+          <t>Оплата за товар по с/ф №1665 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>39856000</v>
+        <v>91833000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
       <c r="C112" s="2" t="n"/>
       <c r="D112" s="2" t="n">
-        <v>5755000</v>
+        <v>3912000</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №168/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №1015 31.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>45611000</v>
+        <v>95745000</v>
       </c>
     </row>
     <row r="113">
@@ -4717,35 +4717,35 @@
       </c>
       <c r="C113" s="2" t="n"/>
       <c r="D113" s="2" t="n">
-        <v>17868000</v>
+        <v>1664000</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Farg'ona Trans Servis XK</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>343426215</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000710731535001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №252/26 от 31.08.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9758 31.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>63479000</v>
+        <v>97409000</v>
       </c>
     </row>
     <row r="114">
@@ -4755,37 +4755,32 @@
       <c r="B114" t="n">
         <v>206</v>
       </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n">
-        <v>15913000</v>
-      </c>
+      <c r="C114" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>367434262</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000527107315001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2842</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>79392000</v>
+        <v>97109000</v>
       </c>
     </row>
     <row r="115">
@@ -4795,138 +4790,143 @@
       <c r="B115" t="n">
         <v>207</v>
       </c>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n">
-        <v>14179000</v>
-      </c>
+      <c r="C115" s="2" t="n">
+        <v>7930000</v>
+      </c>
+      <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Omad Meva Eksport AJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>367434262</t>
+          <t>215107383</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000527107315001</t>
+          <t>20208000575856861001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>SHARTNOMA №246/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №71/26</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>93571000</v>
+        <v>89179000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>7011000</v>
+        <v>6876000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Andijon Mebel XK</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>218610126</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000313104364001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Shartnoma №273/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №62/26, QQS 12%</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>100582000</v>
+        <v>96055000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
-      <c r="C117" s="2" t="n"/>
-      <c r="D117" s="2" t="n">
-        <v>3980000</v>
-      </c>
+      <c r="C117" s="2" t="n">
+        <v>4140000</v>
+      </c>
+      <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>367434262</t>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000527107315001</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №4945 31.08.2026, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №8026</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>104562000</v>
+        <v>91915000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
-      <c r="C118" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n">
+        <v>3888000</v>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Kattaqo'rg'on Plastik MChJ</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>323628962</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000071338667001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4936,201 +4936,206 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>Mahsulot uchun to'lov, shartn. №180/26, QQS 12%</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>104262000</v>
+        <v>95803000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46266</v>
+        <v>46270</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
-      <c r="C119" s="2" t="n"/>
-      <c r="D119" s="2" t="n">
-        <v>3361000</v>
-      </c>
+      <c r="C119" s="2" t="n">
+        <v>24600000</v>
+      </c>
+      <c r="D119" s="2" t="n"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Tong Metall MChJ</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>372693813</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-1067)</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000832203775001</t>
+          <t>16307000371917360417</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №195/26, QQS 12%</t>
+          <t>Kredit shartnomasi L-2024-1067 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>107623000</v>
+        <v>71203000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="n">
-        <v>7505000</v>
+        <v>18255000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №209/26 от 04.09.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №1914 07.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>115128000</v>
+        <v>89458000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
-      <c r="C121" s="2" t="n">
-        <v>13784000</v>
-      </c>
-      <c r="D121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n">
+        <v>7760000</v>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Namangan Meva Eksport AJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>206236289</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000260713386001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2788</t>
+          <t>Tovar uchun to'lov, h/f №1022 07.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>101344000</v>
+        <v>97218000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
-      <c r="C122" s="2" t="n">
-        <v>25656000</v>
-      </c>
-      <c r="D122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n">
+        <v>6816000</v>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Farg'ona Trans Servis XK</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>343426215</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000710731535001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
+          <t>Shartnoma №239/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>75688000</v>
+        <v>104034000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46270</v>
+        <v>46272</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
-      <c r="C123" s="2" t="n">
-        <v>24600000</v>
-      </c>
-      <c r="D123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n">
+        <v>5612000</v>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-1067)</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>16307000371917360417</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-1067 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Оплата по счет-фактуре №1415 за поставленный товар</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>51088000</v>
+        <v>109646000</v>
       </c>
     </row>
     <row r="124">
@@ -5142,35 +5147,35 @@
       </c>
       <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="n">
-        <v>24985000</v>
+        <v>3079000</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Zafar Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>287202980</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000253145244001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №98/26 от 07.09.2026</t>
+          <t>Shartnoma №263/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>76073000</v>
+        <v>112725000</v>
       </c>
     </row>
     <row r="125">
@@ -5180,37 +5185,37 @@
       <c r="B125" t="n">
         <v>217</v>
       </c>
-      <c r="C125" s="2" t="n"/>
-      <c r="D125" s="2" t="n">
-        <v>13055000</v>
-      </c>
+      <c r="C125" s="2" t="n">
+        <v>2604000</v>
+      </c>
+      <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Sarbon Qurilish MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>296114067</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000351645437001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9263 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>Bino ijarasi uchun to'lov sentyabr</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>89128000</v>
+        <v>110121000</v>
       </c>
     </row>
     <row r="126">
@@ -5220,37 +5225,37 @@
       <c r="B126" t="n">
         <v>218</v>
       </c>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n">
-        <v>7198000</v>
-      </c>
+      <c r="C126" s="2" t="n">
+        <v>3442000</v>
+      </c>
+      <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №150/26, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №272/26</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>96326000</v>
+        <v>106679000</v>
       </c>
     </row>
     <row r="127">
@@ -5260,37 +5265,37 @@
       <c r="B127" t="n">
         <v>219</v>
       </c>
-      <c r="C127" s="2" t="n"/>
-      <c r="D127" s="2" t="n">
-        <v>5550000</v>
-      </c>
+      <c r="C127" s="2" t="n">
+        <v>4164000</v>
+      </c>
+      <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №232/26 от 07.09.2026</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №241/26</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>101876000</v>
+        <v>102515000</v>
       </c>
     </row>
     <row r="128">
@@ -5300,263 +5305,258 @@
       <c r="B128" t="n">
         <v>220</v>
       </c>
-      <c r="C128" s="2" t="n"/>
-      <c r="D128" s="2" t="n">
-        <v>5536000</v>
-      </c>
+      <c r="C128" s="2" t="n">
+        <v>25656000</v>
+      </c>
+      <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>351981457</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №250/26 от 07.09.2026</t>
+          <t>ISH HAQI TO'LOVI AVGUST 2026 (PLASTIK KARTALARGA)</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>107412000</v>
+        <v>76859000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46272</v>
+        <v>46276</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
       <c r="C129" s="2" t="n"/>
       <c r="D129" s="2" t="n">
-        <v>4918000</v>
+        <v>25529000</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8881 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №8809 11.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>112330000</v>
+        <v>102388000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46272</v>
+        <v>46276</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>2604000</v>
+        <v>7263000</v>
       </c>
       <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Omad Qurilish MChJ</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>281323691</t>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000893848717001</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Аренда помещения за сентябрь, дог. №77/23</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №213/26</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>109726000</v>
+        <v>95125000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46272</v>
+        <v>46279</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
-      <c r="C131" s="2" t="n">
-        <v>10599000</v>
-      </c>
-      <c r="D131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n">
+        <v>10065000</v>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Xiva Polimer XK</t>
+          <t>Farg'ona Trans Servis XK</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>249672389</t>
+          <t>343426215</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000254901258001</t>
+          <t>20208000710731535001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3118</t>
+          <t>Оплата по счет-фактуре №7113 за поставленный товар</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>99127000</v>
+        <v>105190000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46272</v>
+        <v>46279</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
       <c r="C132" s="2" t="n">
-        <v>24923000</v>
+        <v>1943000</v>
       </c>
       <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Xiva Polimer XK</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>249672389</t>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000254901258001</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №211/26</t>
+          <t>Предоплата за материалы по договору №260/26</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>74204000</v>
+        <v>103247000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>9588000</v>
-      </c>
+      <c r="C133" s="2" t="n">
+        <v>2145000</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Qo'qon Logistik MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>390761727</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000521126139001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9978 от 08.09.2026, в т.ч. НДС 12%</t>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №84/26</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>83792000</v>
+        <v>101102000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
-      <c r="C134" s="2" t="n"/>
-      <c r="D134" s="2" t="n">
-        <v>7854000</v>
-      </c>
+      <c r="C134" s="2" t="n">
+        <v>2355000</v>
+      </c>
+      <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Namangan Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>361039787</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000635048122001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5566,237 +5566,237 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7067</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №34/26</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>91646000</v>
+        <v>98747000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n">
-        <v>3529000</v>
-      </c>
+      <c r="C135" s="2" t="n">
+        <v>17431000</v>
+      </c>
+      <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №188/26, НДС 12%</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №6711</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>95175000</v>
+        <v>81316000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46273</v>
+        <v>46280</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
-      <c r="C136" s="2" t="n">
-        <v>7341000</v>
-      </c>
-      <c r="D136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n">
+        <v>14826000</v>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Shahrisabz Dori-Darmon MChJ</t>
+          <t>Zafar Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>309788781</t>
+          <t>287202980</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000817408794001</t>
+          <t>20208000253145244001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по догвору №279/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №183/26, QQS 12%</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>87834000</v>
+        <v>96142000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46274</v>
+        <v>46280</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
       <c r="C137" s="2" t="n"/>
       <c r="D137" s="2" t="n">
-        <v>18257000</v>
+        <v>6465000</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Andijon Mebel XK</t>
+          <t>Zafar Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>218610126</t>
+          <t>287202980</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000313104364001</t>
+          <t>20208000253145244001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3126 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3518 15.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>106091000</v>
+        <v>102607000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="n">
-        <v>39519000</v>
+        <v>4953000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Tong Metall MChJ</t>
+          <t>Kattaqo'rg'on Plastik MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>372693813</t>
+          <t>323628962</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000832203775001</t>
+          <t>20208000071338667001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №189/26, НДС 12%</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №14/26, НДС 12%</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>145610000</v>
+        <v>107560000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
-      <c r="C139" s="2" t="n">
-        <v>25311000</v>
-      </c>
-      <c r="D139" s="2" t="n"/>
+      <c r="C139" s="2" t="n"/>
+      <c r="D139" s="2" t="n">
+        <v>4206000</v>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Durdona Mehmonxona MChJ</t>
+          <t>Zafar Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>356394094</t>
+          <t>287202980</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000768404857001</t>
+          <t>20208000253145244001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №54/26, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №250/26, QQS 12%</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>120299000</v>
+        <v>111766000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
-      <c r="C140" s="2" t="n"/>
-      <c r="D140" s="2" t="n">
-        <v>10300000</v>
-      </c>
+      <c r="C140" s="2" t="n">
+        <v>2440000</v>
+      </c>
+      <c r="D140" s="2" t="n"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer MChJ</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>312872029</t>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000012531452001</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -5806,557 +5806,557 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №107/26, НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №3593</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>130599000</v>
+        <v>109326000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
-      <c r="C141" s="2" t="n"/>
-      <c r="D141" s="2" t="n">
-        <v>4128000</v>
-      </c>
+      <c r="C141" s="2" t="n">
+        <v>3498000</v>
+      </c>
+      <c r="D141" s="2" t="n"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Tong Metall MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>372693813</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000832203775001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5467 за поставленный товар</t>
+          <t>Социальный налог за август 2026 г.</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>134727000</v>
+        <v>105828000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
-      <c r="C142" s="2" t="n"/>
-      <c r="D142" s="2" t="n">
-        <v>2683000</v>
-      </c>
+      <c r="C142" s="2" t="n">
+        <v>3498000</v>
+      </c>
+      <c r="D142" s="2" t="n"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №296/26, QQS 12%</t>
+          <t>JShDS avgust oyi uchun</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>137410000</v>
+        <v>102330000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="n">
-        <v>6511000</v>
+        <v>3321000</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3809 14.09.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №41/26, QQS 12%</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>143921000</v>
+        <v>105651000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46279</v>
+        <v>46282</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
       <c r="C144" s="2" t="n"/>
       <c r="D144" s="2" t="n">
-        <v>5668000</v>
+        <v>73729000</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Toshkent Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>274534012</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000445565106001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №96/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №95/26, QQS 12%</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>149589000</v>
+        <v>179380000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46279</v>
+        <v>46282</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>4013000</v>
-      </c>
+      <c r="C145" s="2" t="n">
+        <v>9095000</v>
+      </c>
+      <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Bahor Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>339409477</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000840485720001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №109/26, НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №243/26</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>153602000</v>
+        <v>170285000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
-      <c r="C146" s="2" t="n">
-        <v>3498000</v>
-      </c>
-      <c r="D146" s="2" t="n"/>
+      <c r="C146" s="2" t="n"/>
+      <c r="D146" s="2" t="n">
+        <v>5762000</v>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zafar Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>287202980</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000253145244001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Социальный налог за август 2026 г.</t>
+          <t>Оплата за товар по счет-фактуре №9895 от 18.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>150104000</v>
+        <v>176047000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
-      <c r="C147" s="2" t="n">
-        <v>3498000</v>
-      </c>
-      <c r="D147" s="2" t="n"/>
+      <c r="C147" s="2" t="n"/>
+      <c r="D147" s="2" t="n">
+        <v>3752000</v>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за август 2026 г.</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2034 18.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>146606000</v>
+        <v>179799000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B148" t="n">
         <v>240</v>
       </c>
       <c r="C148" s="2" t="n">
-        <v>8916000</v>
+        <v>33803000</v>
       </c>
       <c r="D148" s="2" t="n"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Xiva Polimer XK</t>
+          <t>Nukus Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>249672389</t>
+          <t>213000939</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000254901258001</t>
+          <t>20208000057304502001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №1951</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №67/26</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>137690000</v>
+        <v>145996000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="B149" t="n">
         <v>241</v>
       </c>
-      <c r="C149" s="2" t="n">
-        <v>9975000</v>
-      </c>
-      <c r="D149" s="2" t="n"/>
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="2" t="n">
+        <v>10495000</v>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Xiva Polimer XK</t>
+          <t>Kattaqo'rg'on Plastik MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>249672389</t>
+          <t>323628962</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000254901258001</t>
+          <t>20208000071338667001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №122/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8839</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>127715000</v>
+        <v>156491000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B150" t="n">
         <v>242</v>
       </c>
       <c r="C150" s="2" t="n"/>
       <c r="D150" s="2" t="n">
-        <v>22136000</v>
+        <v>4699000</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Zafar Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>287202980</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000253145244001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7304 от 15.09.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №8/26, QQS 12%</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>149851000</v>
+        <v>161190000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B151" t="n">
         <v>243</v>
       </c>
-      <c r="C151" s="2" t="n"/>
-      <c r="D151" s="2" t="n">
-        <v>2781000</v>
-      </c>
+      <c r="C151" s="2" t="n">
+        <v>211518000</v>
+      </c>
+      <c r="D151" s="2" t="n"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Omad Meva Eksport AJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>215107383</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000575856861001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №509 от 15.09.2026, в т.ч. НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartn. №243/26, QQS bilan</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>152632000</v>
+        <v>-50328000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
-        <v>46280</v>
+        <v>46288</v>
       </c>
       <c r="B152" t="n">
         <v>244</v>
       </c>
-      <c r="C152" s="2" t="n">
-        <v>6187000</v>
-      </c>
-      <c r="D152" s="2" t="n"/>
+      <c r="C152" s="2" t="n"/>
+      <c r="D152" s="2" t="n">
+        <v>14402000</v>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Nihol Oziq-ovqat Savdo XK</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>336227780</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000612992396001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9431</t>
+          <t>Mahsulot uchun to'lov, shartn. №263/26, QQS 12%</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>146445000</v>
+        <v>-35926000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="B153" t="n">
         <v>245</v>
       </c>
-      <c r="C153" s="2" t="n">
-        <v>6089000</v>
-      </c>
-      <c r="D153" s="2" t="n"/>
+      <c r="C153" s="2" t="n"/>
+      <c r="D153" s="2" t="n">
+        <v>7832000</v>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Xiva Polimer XK</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>249672389</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000254901258001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №112/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2038</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>140356000</v>
+        <v>-28094000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="B154" t="n">
         <v>246</v>
       </c>
-      <c r="C154" s="2" t="n">
-        <v>11098000</v>
-      </c>
-      <c r="D154" s="2" t="n"/>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="2" t="n">
+        <v>3063000</v>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Xiva Polimer XK</t>
+          <t>Toshkent Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>249672389</t>
+          <t>274534012</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000254901258001</t>
+          <t>20208000445565106001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6366,117 +6366,117 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7355</t>
+          <t>Shartnoma №200/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>129258000</v>
+        <v>-25031000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="B155" t="n">
         <v>247</v>
       </c>
       <c r="C155" s="2" t="n">
-        <v>20934000</v>
+        <v>1627000</v>
       </c>
       <c r="D155" s="2" t="n"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Nihol Oziq-ovqat Savdo XK</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>336227780</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000612992396001</t>
+          <t>20208000635963108001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8804</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>108324000</v>
+        <v>-26658000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="B156" t="n">
         <v>248</v>
       </c>
-      <c r="C156" s="2" t="n"/>
-      <c r="D156" s="2" t="n">
-        <v>2190000</v>
-      </c>
+      <c r="C156" s="2" t="n">
+        <v>4402000</v>
+      </c>
+      <c r="D156" s="2" t="n"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №241/26, НДС 12%</t>
+          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>110514000</v>
+        <v>-31060000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="B157" t="n">
         <v>249</v>
       </c>
       <c r="C157" s="2" t="n"/>
       <c r="D157" s="2" t="n">
-        <v>4623000</v>
+        <v>5772000</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Navro'z Trans Servis MChJ</t>
+          <t>Farg'ona Trans Servis XK</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>367434262</t>
+          <t>343426215</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20208000527107315001</t>
+          <t>20208000710731535001</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -6486,1191 +6486,431 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №4250 от 18.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №8042 от 25.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>115137000</v>
+        <v>-25288000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="B158" t="n">
         <v>250</v>
       </c>
-      <c r="C158" s="2" t="n">
-        <v>9740000</v>
-      </c>
-      <c r="D158" s="2" t="n"/>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n">
+        <v>2947000</v>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Durdona Mehmonxona MChJ</t>
+          <t>Urganch Non MChJ</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>356394094</t>
+          <t>361012663</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000768404857001</t>
+          <t>20208000310436449001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №8361</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4927</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>105397000</v>
+        <v>-22341000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B159" t="n">
         <v>251</v>
       </c>
       <c r="C159" s="2" t="n"/>
       <c r="D159" s="2" t="n">
-        <v>9193000</v>
+        <v>13471000</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №192/26 от 21.09.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8391</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>114590000</v>
+        <v>-8870000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B160" t="n">
         <v>252</v>
       </c>
       <c r="C160" s="2" t="n"/>
       <c r="D160" s="2" t="n">
-        <v>4874000</v>
+        <v>13407000</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №981 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5752 28.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>119464000</v>
+        <v>4537000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B161" t="n">
         <v>253</v>
       </c>
       <c r="C161" s="2" t="n"/>
       <c r="D161" s="2" t="n">
-        <v>4121000</v>
+        <v>10982000</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Afrosiyob Polimer MChJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>312872029</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>20208000012531452001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №253/26 от 21.09.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №158/26, QQS 12%</t>
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>123585000</v>
+        <v>15519000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B162" t="n">
         <v>254</v>
       </c>
       <c r="C162" s="2" t="n"/>
       <c r="D162" s="2" t="n">
-        <v>3008000</v>
+        <v>7741000</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>351981457</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №863 от 21.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №782 за поставленный товар</t>
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>126593000</v>
+        <v>23260000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n">
-        <v>46286</v>
+        <v>46294</v>
       </c>
       <c r="B163" t="n">
         <v>255</v>
       </c>
       <c r="C163" s="2" t="n"/>
       <c r="D163" s="2" t="n">
-        <v>2326000</v>
+        <v>55259000</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Yulduz Logistik MChJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>324503118</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>20208000824779806001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3151</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6563</t>
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>128919000</v>
+        <v>78519000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n">
-        <v>46286</v>
+        <v>46294</v>
       </c>
       <c r="B164" t="n">
         <v>256</v>
       </c>
       <c r="C164" s="2" t="n"/>
       <c r="D164" s="2" t="n">
-        <v>1849000</v>
+        <v>4935000</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Tong Metall MChJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>372693813</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>20208000832203775001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4192 за поставленный товар</t>
+          <t>Shartnoma №56/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>130768000</v>
+        <v>83454000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n">
-        <v>46286</v>
+        <v>46294</v>
       </c>
       <c r="B165" t="n">
         <v>257</v>
       </c>
-      <c r="C165" s="2" t="n">
-        <v>10990000</v>
-      </c>
-      <c r="D165" s="2" t="n"/>
+      <c r="C165" s="2" t="n"/>
+      <c r="D165" s="2" t="n">
+        <v>3252000</v>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Shahrisabz Dori-Darmon MChJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>309788781</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>20208000817408794001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>TOVARLAR UCHUN TO'LOV H/F №3749</t>
+          <t>Оплата за товар по счет-фактуре №546 от 29.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>119778000</v>
+        <v>86706000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n">
-        <v>46286</v>
+        <v>46295</v>
       </c>
       <c r="B166" t="n">
         <v>258</v>
       </c>
-      <c r="C166" s="2" t="n">
-        <v>17642000</v>
-      </c>
-      <c r="D166" s="2" t="n"/>
+      <c r="C166" s="2" t="n"/>
+      <c r="D166" s="2" t="n">
+        <v>3694000</v>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Durdona Mehmonxona MChJ</t>
+          <t>Qo'qon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>356394094</t>
+          <t>298145746</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>20208000768404857001</t>
+          <t>20208000175503570001</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №92/26 от 21.09.2026, НДС 12%</t>
+          <t>Оплата за продукцию по дог. №208/26, НДС 12%</t>
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>102136000</v>
+        <v>90400000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n">
-        <v>46287</v>
+        <v>46295</v>
       </c>
       <c r="B167" t="n">
         <v>259</v>
       </c>
-      <c r="C167" s="2" t="n"/>
-      <c r="D167" s="2" t="n">
-        <v>2642000</v>
-      </c>
+      <c r="C167" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D167" s="2" t="n"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Afrosiyob Agro AJ</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>351981457</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>20208000621755035001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №4780 от 22.09.2026, в т.ч. НДС 12%</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>104778000</v>
+        <v>90100000</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="3" t="n">
-        <v>46287</v>
-      </c>
-      <c r="B168" t="n">
-        <v>260</v>
-      </c>
-      <c r="C168" s="2" t="n"/>
-      <c r="D168" s="2" t="n">
-        <v>2202000</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Tong Metall MChJ</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>372693813</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>20208000832203775001</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9650</t>
-        </is>
-      </c>
-      <c r="J168" s="2" t="n">
-        <v>106980000</v>
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Итого обороты:</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="n">
+        <v>1088283000</v>
+      </c>
+      <c r="D168" s="4" t="n">
+        <v>1078983000</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="3" t="n">
-        <v>46287</v>
-      </c>
-      <c r="B169" t="n">
-        <v>261</v>
-      </c>
-      <c r="C169" s="2" t="n">
-        <v>16472000</v>
-      </c>
-      <c r="D169" s="2" t="n"/>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Xiva Polimer XK</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>249672389</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>20208000254901258001</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №227/26, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="n">
-        <v>90508000</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="B170" t="n">
-        <v>262</v>
-      </c>
-      <c r="C170" s="2" t="n"/>
-      <c r="D170" s="2" t="n">
-        <v>10603000</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Andijon Mebel XK</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>218610126</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>20208000313104364001</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartn. №287/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J170" s="2" t="n">
-        <v>101111000</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="B171" t="n">
-        <v>263</v>
-      </c>
-      <c r="C171" s="2" t="n">
-        <v>4260000</v>
-      </c>
-      <c r="D171" s="2" t="n"/>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>НДС за август 2026 г.</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="n">
-        <v>96851000</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B172" t="n">
-        <v>264</v>
-      </c>
-      <c r="C172" s="2" t="n"/>
-      <c r="D172" s="2" t="n">
-        <v>3222000</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Afrosiyob Agro AJ</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>351981457</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>20208000621755035001</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №8657</t>
-        </is>
-      </c>
-      <c r="J172" s="2" t="n">
-        <v>100073000</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B173" t="n">
-        <v>265</v>
-      </c>
-      <c r="C173" s="2" t="n"/>
-      <c r="D173" s="2" t="n">
-        <v>2108000</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Afrosiyob Polimer MChJ</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>312872029</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>20208000012531452001</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №5283 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="n">
-        <v>102181000</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B174" t="n">
-        <v>266</v>
-      </c>
-      <c r="C174" s="2" t="n">
-        <v>1627000</v>
-      </c>
-      <c r="D174" s="2" t="n"/>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>200933985</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>20208000737739460001</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>Elektr energiyasi uchun to'lov</t>
-        </is>
-      </c>
-      <c r="J174" s="2" t="n">
-        <v>100554000</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B175" t="n">
-        <v>267</v>
-      </c>
-      <c r="C175" s="2" t="n">
-        <v>22410000</v>
-      </c>
-      <c r="D175" s="2" t="n"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Nihol Oziq-ovqat Savdo XK</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>336227780</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>20208000612992396001</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>Оплата за транспортные услуги по дог. №61/26</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="n">
-        <v>78144000</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B176" t="n">
-        <v>268</v>
-      </c>
-      <c r="C176" s="2" t="n"/>
-      <c r="D176" s="2" t="n">
-        <v>9634000</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Afrosiyob Agro AJ</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>351981457</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>20208000621755035001</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №278/26 от 28.09.2026</t>
-        </is>
-      </c>
-      <c r="J176" s="2" t="n">
-        <v>87778000</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B177" t="n">
-        <v>269</v>
-      </c>
-      <c r="C177" s="2" t="n">
-        <v>6043000</v>
-      </c>
-      <c r="D177" s="2" t="n"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Xiva Polimer XK</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>249672389</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>20208000254901258001</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>Оплата за транспортные услуги по договору №194/26</t>
-        </is>
-      </c>
-      <c r="J177" s="2" t="n">
-        <v>81735000</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B178" t="n">
-        <v>270</v>
-      </c>
-      <c r="C178" s="2" t="n">
-        <v>13297000</v>
-      </c>
-      <c r="D178" s="2" t="n"/>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Xiva Polimer XK</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>249672389</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>20208000254901258001</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>Оплата за транспортные услуги по договору №123/26</t>
-        </is>
-      </c>
-      <c r="J178" s="2" t="n">
-        <v>68438000</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B179" t="n">
-        <v>271</v>
-      </c>
-      <c r="C179" s="2" t="n">
-        <v>39880000</v>
-      </c>
-      <c r="D179" s="2" t="n"/>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Nihol Oziq-ovqat Savdo XK</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>336227780</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>20208000612992396001</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>Предоплата за материалы по договору №298/26</t>
-        </is>
-      </c>
-      <c r="J179" s="2" t="n">
-        <v>28558000</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B180" t="n">
-        <v>272</v>
-      </c>
-      <c r="C180" s="2" t="n"/>
-      <c r="D180" s="2" t="n">
-        <v>4498000</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Afrosiyob Agro AJ</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>351981457</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>20208000621755035001</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №777 от 29.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J180" s="2" t="n">
-        <v>33056000</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B181" t="n">
-        <v>273</v>
-      </c>
-      <c r="C181" s="2" t="n"/>
-      <c r="D181" s="2" t="n">
-        <v>3542000</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Afrosiyob Agro AJ</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>351981457</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>20208000621755035001</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №4052 ОТ 29.09.2026, В Т.Ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J181" s="2" t="n">
-        <v>36598000</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B182" t="n">
-        <v>274</v>
-      </c>
-      <c r="C182" s="2" t="n"/>
-      <c r="D182" s="2" t="n">
-        <v>2375000</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Afrosiyob Agro AJ</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>351981457</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>20208000621755035001</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5390</t>
-        </is>
-      </c>
-      <c r="J182" s="2" t="n">
-        <v>38973000</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B183" t="n">
-        <v>275</v>
-      </c>
-      <c r="C183" s="2" t="n"/>
-      <c r="D183" s="2" t="n">
-        <v>52734000</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Navro'z Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>367434262</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>20208000527107315001</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №3915 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
-        </is>
-      </c>
-      <c r="J183" s="2" t="n">
-        <v>91707000</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B184" t="n">
-        <v>276</v>
-      </c>
-      <c r="C184" s="2" t="n"/>
-      <c r="D184" s="2" t="n">
-        <v>20184000</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Tong Metall MChJ</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>372693813</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>20208000832203775001</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, h/f №7257 30.09.2026, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J184" s="2" t="n">
-        <v>111891000</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B185" t="n">
-        <v>277</v>
-      </c>
-      <c r="C185" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D185" s="2" t="n"/>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Bodomzor Bank ATB</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за сентябрь</t>
-        </is>
-      </c>
-      <c r="J185" s="2" t="n">
-        <v>111591000</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B186" t="n">
-        <v>278</v>
-      </c>
-      <c r="C186" s="2" t="n">
-        <v>21491000</v>
-      </c>
-      <c r="D186" s="2" t="n"/>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Omad Sut Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>353997534</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>20208000463310668001</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>Оплата за товары согласно счет-фактуре №61</t>
-        </is>
-      </c>
-      <c r="J186" s="2" t="n">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Исходящий остаток на 30.09.2026:</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="n">
         <v>90100000</v>
       </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Итого обороты:</t>
-        </is>
-      </c>
-      <c r="C187" s="4" t="n">
-        <v>1098429000</v>
-      </c>
-      <c r="D187" s="4" t="n">
-        <v>1089129000</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Исходящий остаток на 30.09.2026:</t>
-        </is>
-      </c>
-      <c r="C188" s="4" t="n">
-        <v>90100000</v>
-      </c>
-      <c r="D188" s="4" t="n"/>
+      <c r="D169" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
